--- a/受试者信息收集表.xlsx
+++ b/受试者信息收集表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20148" windowHeight="17700"/>
+    <workbookView windowWidth="20796" windowHeight="10044"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="5" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Subject_ID</t>
   </si>
@@ -36,6 +36,24 @@
   </si>
   <si>
     <t>02lfm</t>
+  </si>
+  <si>
+    <t>03zhangyining</t>
+  </si>
+  <si>
+    <t>04qiuyu</t>
+  </si>
+  <si>
+    <t>05heyaping</t>
+  </si>
+  <si>
+    <t>06kang</t>
+  </si>
+  <si>
+    <t>07wangquanhui</t>
+  </si>
+  <si>
+    <t>08songziyi</t>
   </si>
   <si>
     <t>固定座椅高度</t>
@@ -1038,12 +1056,24 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
@@ -1051,7 +1081,7 @@
     </row>
     <row r="2" ht="19" customHeight="1" spans="1:13">
       <c r="A2" s="2" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B2" s="2">
         <v>460</v>
@@ -1059,12 +1089,24 @@
       <c r="C2" s="2">
         <v>460</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
+      <c r="D2" s="2">
+        <v>460</v>
+      </c>
+      <c r="E2" s="2">
+        <v>460</v>
+      </c>
+      <c r="F2" s="2">
+        <v>460</v>
+      </c>
+      <c r="G2" s="2">
+        <v>460</v>
+      </c>
+      <c r="H2" s="2">
+        <v>460</v>
+      </c>
+      <c r="I2" s="2">
+        <v>460</v>
+      </c>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
@@ -1072,7 +1114,7 @@
     </row>
     <row r="3" ht="19" customHeight="1" spans="1:13">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B3" s="2">
         <v>750</v>
@@ -1080,12 +1122,24 @@
       <c r="C3" s="2">
         <v>750</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
+      <c r="D3" s="2">
+        <v>750</v>
+      </c>
+      <c r="E3" s="2">
+        <v>750</v>
+      </c>
+      <c r="F3" s="2">
+        <v>750</v>
+      </c>
+      <c r="G3" s="2">
+        <v>750</v>
+      </c>
+      <c r="H3" s="2">
+        <v>750</v>
+      </c>
+      <c r="I3" s="2">
+        <v>750</v>
+      </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
@@ -1093,7 +1147,7 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B4">
         <v>235</v>
@@ -1104,18 +1158,36 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="2" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B5">
         <v>815</v>
       </c>
       <c r="C5">
         <v>820</v>
+      </c>
+      <c r="D5">
+        <v>815</v>
+      </c>
+      <c r="E5">
+        <v>870</v>
+      </c>
+      <c r="F5">
+        <v>875</v>
+      </c>
+      <c r="G5">
+        <v>820</v>
+      </c>
+      <c r="H5">
+        <v>850</v>
+      </c>
+      <c r="I5">
+        <v>845</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B6">
         <f>B5-B3</f>
@@ -1125,21 +1197,63 @@
         <f>C5-C3</f>
         <v>70</v>
       </c>
+      <c r="D6">
+        <f t="shared" ref="D6:I6" si="0">D5-D3</f>
+        <v>65</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="0"/>
+        <v>120</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>125</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="0"/>
+        <v>95</v>
+      </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B7">
         <v>715</v>
       </c>
       <c r="C7">
         <v>720</v>
+      </c>
+      <c r="D7">
+        <v>715</v>
+      </c>
+      <c r="E7">
+        <v>770</v>
+      </c>
+      <c r="F7">
+        <v>775</v>
+      </c>
+      <c r="G7">
+        <v>720</v>
+      </c>
+      <c r="H7">
+        <v>750</v>
+      </c>
+      <c r="I7">
+        <v>745</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B8">
         <f>B7-B3</f>
@@ -1148,6 +1262,30 @@
       <c r="C8">
         <f>C7-C3</f>
         <v>-30</v>
+      </c>
+      <c r="D8">
+        <f t="shared" ref="D8:I8" si="1">D7-D3</f>
+        <v>-35</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="1"/>
+        <v>-30</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="1"/>
+        <v>-5</v>
       </c>
     </row>
   </sheetData>
